--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cbf718cd9aac73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Managed Service Change Analyst Specialists: Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5aca710daed1ba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Managed Service Change Analyst Specialists: Site Reliability Engineer (SRE)</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5aca710daed1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
+          <t>Senior Data engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
+          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8307e07dc984427c</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=8307e07dc984427c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,52 +2831,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Databricks Architect</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Solvstaff</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
@@ -3303,25 +3303,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLOps Engineer II (Remote)</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>DevOps Software Engineer Specialists</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer Specialists</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Womble Bond Dickinson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Oracle Database Administrator</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git, Datadog</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5694d420c9003d</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - CostCheck</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BlueSight</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Security &amp; DevSecOps Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Application Security &amp; DevSecOps Architect</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Medical Mutual of Ohio</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Financial Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 1</t>
+          <t>Java Developer - HYBRID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e1d20485e6d34c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
@@ -2743,52 +2743,52 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,69 +2796,69 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Via Separations</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Via Separations</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III, Development</t>
+          <t>Senior Backend Engineer, Core APIs</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIs</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
+          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Western Alliance Bank</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer Specialists</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Application Security &amp; DevSecOps Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medical Mutual of Ohio</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Snowflake DBT Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Sr. AI Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Application Security &amp; DevSecOps Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Engineer - International Project</t>
+          <t>Financial Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Java Developer - HYBRID</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
+          <t>Java Developer - HYBRID</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,87 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
+          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - International Project</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Western Alliance Bank</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, DynamoDB, MicroStrategy, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=23c2424743b671f3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Womble Bond Dickinson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake DBT Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,24 +3881,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Sr. AI Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>Application Security &amp; DevSecOps Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Application Security &amp; DevSecOps Architect</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medical Mutual of Ohio</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Financial Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Java Developer - HYBRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Developer - HYBRID</t>
+          <t>DevOps Engineer - International Project</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,76 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Sr. Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - International Project</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meridian Systematics</t>
+          <t>RectorSeal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f4cd04f1d7226b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a61d914fd12568</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8307e07dc984427c</t>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8307e07dc984427c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Via Separations</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIs</t>
+          <t>Software Engineer Sr (Java)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Senior Application System Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Via Separations</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,94 +3366,94 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, DynamoDB, MicroStrategy, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c2424743b671f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI</t>
+          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
+          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Sigma Software Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3807,81 +3807,81 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Womble Bond Dickinson</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,59 +3891,59 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Application Security &amp; DevSecOps Architect</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Medical Mutual of Ohio</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,29 +3951,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
+          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. AI Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Application Security &amp; DevSecOps Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,19 +4101,19 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4122,46 +4122,46 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java Developer - HYBRID</t>
+          <t>Snowflake DBT Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,75 +4171,355 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd52425ff4c524df</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>Ansible Automation Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Pacific Life</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior OpenTelemetry Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Woodland Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>V4C.ai</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Financial Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Analyst / Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Datavault AI</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>DevOps Engineer - International Project</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Seattle, WA, US USA</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D117" t="n">
         <v>10.4</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Temporary Worker</t>
+          <t>Data/Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Managed Service Change Analyst Specialists: Site Reliability Engineer (SRE)</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5aca710daed1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8307e07dc984427c</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer Sr (Java)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Application System Engineer</t>
+          <t>Software Engineer Sr (Java)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,69 +2971,69 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Application System Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Via Separations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Via Separations</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,112 +3741,112 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sigma Software Group</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sigma Software Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,129 +3926,129 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Womble Bond Dickinson</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>FocusPointSAP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, GitHub Actions, Docker, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=b64c9105e7675d73</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Application Security &amp; DevSecOps Architect</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Medical Mutual of Ohio</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
+          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a22db44a8888801</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. AI Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,124 +4276,124 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior OpenTelemetry Engineer</t>
+          <t>Snowflake DBT Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4402,46 +4402,46 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer - International Project</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,227 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior OpenTelemetry Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Woodland Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>V4C.ai</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Financial Data Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Analyst / Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Datavault AI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - CSS, AIP and HPX Analytics</t>
+          <t>Data/Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Hadoop, Hive</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a78dd582651cf84</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RectorSeal</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a61d914fd12568</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cbf718cd9aac73</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Development Ops Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, HBase, Spark, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43701e8a621c350</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Temporary Worker</t>
+          <t>cloud solution engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79b9ae386c30e15</t>
+          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data/Analytics Engineer</t>
+          <t>Senior Data engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator - Computing Services</t>
+          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cbf718cd9aac73</t>
+          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data engineer</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,94 +2736,94 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Sr (Java)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Application System Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer Sr (Java)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Application System Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Via Separations</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Via Separations</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,69 +3111,69 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Canada, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Cable One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Linear Advertising Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, MySQL, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59abce8159d1399a</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Software Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>AtkinsRéalis</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,94 +3821,94 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Sigma Software Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sigma Software Group</t>
+          <t>Womble Bond Dickinson</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
         </is>
       </c>
     </row>
@@ -4003,25 +4003,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Senior Software Engineer - Interop</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=877588695da3d179</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer: Ai Enablement and Agentic Develoopment</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Excellis Consulting Corporation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9aedd178e13717</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Sr. AI Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake DBT Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb0d78e2e37acc8</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,17 +4721,157 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Datavault AI</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-01.xlsx
+++ b/results/job_matches_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data/Analytics Engineer</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
+          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator - Computing Services</t>
+          <t>Data/Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6cbf718cd9aac73</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6cbf718cd9aac73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cloud solution engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data engineer</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
+          <t>cloud solution engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior Data engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c1dbb6abf6b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac5da3fd48d3bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0aef032347c64</t>
+          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccad7734d3de242e</t>
+          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da7530d86938f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60678a704bf64f4</t>
+          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eb953e60060a34</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cce728591c8fea</t>
+          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b7f169148c17f4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4420962f77cb95c</t>
+          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d0e018aa48bdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309c9cbc059c8ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0124a9f6fa89c12</t>
+          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d66c118c15ff21</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362bb4eb6549c026</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa644ea1538f074</t>
+          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5abf729578441a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d12dad81a13d04</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc53707841ba936a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc193932d24f51e</t>
+          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1081afe0268e25</t>
+          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618c638da5ec0631</t>
+          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b95de04181ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f85db5b41871e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812b2c544d0156f</t>
+          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd44e6a3d4a51495</t>
+          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e9426795f88b93</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e1bbbbceabf0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7c36aeea5d079</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5cb3ec873308</t>
+          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a12a47cb0876b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947c42dd2b306f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae39f02d0f294bea</t>
+          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c142e3d444448160</t>
+          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74828eb28979387</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b039e5678ef59a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2ac3d700e41e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6919551aa68a5394</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb2824c263d220</t>
+          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5345860f08559</t>
+          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80b7621b9e2f913</t>
+          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823870a08a1db65</t>
+          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d055e8ad0c2a80</t>
+          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382778aa87acaf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dfc5821f41ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd54d92f448b989</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424df3bb9b87f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3eb31df717e0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d29200f69d46c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc844d8227e0c722</t>
+          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4c68521a1f351d</t>
+          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f864b7c17caee013</t>
+          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736de4d3974ebb73</t>
+          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f138b685e2cb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231ded9c25f76bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer Sr (Java)</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c1b0c25c4f79fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Application System Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=be6eb56bdb2b30c9</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Via Separations</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=2a80b58619ce00bf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Application System Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d25899ee1f9c7e2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
+          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,77 +3111,77 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Via Separations</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e7b169aba6ca36</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=12f702690763987d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Sweep)</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
+          <t>https://www.indeed.com/viewjob?jk=c0bbe20f85dfd2a2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada, KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=210c0c0b6772ab92</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,29 +3601,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr BI Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cherokee Nation Businesses</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Catoosa, OK, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,42 +3811,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sigma Software Group</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Womble Bond Dickinson</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8fb71cef7c6797</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Splunk, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd85dafda269f4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FocusPointSAP</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, GitHub Actions, Docker, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64c9105e7675d73</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,102 +4031,102 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Interop</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877588695da3d179</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Developer: Ai Enablement and Agentic Develoopment</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Excellis Consulting Corporation</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9aedd178e13717</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. AI Architect</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior OpenTelemetry Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,102 +4591,102 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,110 +4766,1860 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Canada, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cable One</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa3b20b5d3e05c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>LSEG (London Stock Exchange Group)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Databricks Data Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Data Ninjas Inc.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CERTIFID</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CERTIFID</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>WilmerHale</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3766eea758ba5c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI Solutions Software Developer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI Specialist</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kenneth Copeland Ministries</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Newark, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sigma Software Group</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8987bf2e6d7d503e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FocusPointSAP</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, GitHub Actions, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b64c9105e7675d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MHK TECH</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Full Stack Software Developer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Sr. AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Grace Hill</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e61e632ba68e42b</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sr. AI Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c30f9895c7415caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Cyber Security Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Bectran Inc</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior AI App Developer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Precision CastParts</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Clackamas, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Snowflake DBT Developer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Data Engineer/Sr. BI Developer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Bharathvio Technologies</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Kent, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior OpenTelemetry Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Woodland Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>V4C.ai</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Financial Data Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Data Analyst / Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Highmark Health</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbcc02e72366f37a</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Datavault AI</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9677be782841e9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524cc51479b950ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
         <is>
           <t>Clever Devices</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>Woodbury, NY, US USA</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D177" t="n">
         <v>10.4</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>
